--- a/Outputs/Scenarios/PtX_demand_DK_Electrification.xlsx
+++ b/Outputs/Scenarios/PtX_demand_DK_Electrification.xlsx
@@ -809,7 +809,7 @@
         <v>0.003168171690874954</v>
       </c>
       <c r="I10" t="n">
-        <v>0.006282090740889801</v>
+        <v>0.0062820907408898</v>
       </c>
       <c r="J10" t="n">
         <v>5.039905455642576e-05</v>
@@ -846,7 +846,7 @@
         <v>0.0288833029545226</v>
       </c>
       <c r="I11" t="n">
-        <v>0.03983217865006451</v>
+        <v>0.0398321786500645</v>
       </c>
       <c r="J11" t="n">
         <v>0.0003050655832605</v>
@@ -1568,7 +1568,7 @@
         <v>2050</v>
       </c>
       <c r="C31" t="n">
-        <v>1.711905978853132e-05</v>
+        <v>1.711905978853133e-05</v>
       </c>
       <c r="D31" t="n">
         <v>0.0009001555366186996</v>
@@ -1975,7 +1975,7 @@
         <v>2050</v>
       </c>
       <c r="C42" t="n">
-        <v>8.559529894265662e-06</v>
+        <v>8.559529894265664e-06</v>
       </c>
       <c r="D42" t="n">
         <v>0.0007201244292949598</v>
@@ -1990,7 +1990,7 @@
         <v>0.000100180253935109</v>
       </c>
       <c r="H42" t="n">
-        <v>0.002971384824855994</v>
+        <v>0.002971384824855993</v>
       </c>
       <c r="I42" t="n">
         <v>0.0009573253436375435</v>

--- a/Outputs/Scenarios/PtX_demand_DK_Electrification.xlsx
+++ b/Outputs/Scenarios/PtX_demand_DK_Electrification.xlsx
@@ -1037,7 +1037,7 @@
         <v>0.0004952914075622283</v>
       </c>
       <c r="K16" t="n">
-        <v>0.002646073581422955</v>
+        <v>0.002877396064777138</v>
       </c>
     </row>
     <row r="17">
@@ -1074,7 +1074,7 @@
         <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>0.0004410122635704925</v>
+        <v>0.0005781945420258964</v>
       </c>
     </row>
     <row r="18">
@@ -1111,7 +1111,7 @@
         <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>0.00176404905428197</v>
+        <v>0.002312778168103585</v>
       </c>
     </row>
     <row r="19">
@@ -1148,7 +1148,7 @@
         <v>0</v>
       </c>
       <c r="K19" t="n">
-        <v>0.002646073581422955</v>
+        <v>0.002312778168103585</v>
       </c>
     </row>
     <row r="20">
@@ -1333,7 +1333,7 @@
         <v>3.969274576932214e-05</v>
       </c>
       <c r="K24" t="n">
-        <v>0.003687979208939731</v>
+        <v>0.003620701055041953</v>
       </c>
     </row>
     <row r="25">
@@ -1370,7 +1370,7 @@
         <v>0.0002402602736480331</v>
       </c>
       <c r="K25" t="n">
-        <v>0.03584161762163881</v>
+        <v>0.03518777503476934</v>
       </c>
     </row>
     <row r="26">
@@ -1481,7 +1481,7 @@
         <v>7.136310795228682e-06</v>
       </c>
       <c r="K28" t="n">
-        <v>0.0004410122635704925</v>
+        <v>0.0005781945420258964</v>
       </c>
     </row>
     <row r="29">
@@ -1555,7 +1555,7 @@
         <v>0.0007332186289504282</v>
       </c>
       <c r="K30" t="n">
-        <v>0.01555630259572048</v>
+        <v>0.01550752234985518</v>
       </c>
     </row>
     <row r="31">
@@ -1592,7 +1592,7 @@
         <v>0</v>
       </c>
       <c r="K31" t="n">
-        <v>0.002592717099286747</v>
+        <v>0.003116138543730626</v>
       </c>
     </row>
     <row r="32">
@@ -1629,7 +1629,7 @@
         <v>0</v>
       </c>
       <c r="K32" t="n">
-        <v>0.01037086839714699</v>
+        <v>0.0124645541749225</v>
       </c>
     </row>
     <row r="33">
@@ -1666,7 +1666,7 @@
         <v>0</v>
       </c>
       <c r="K33" t="n">
-        <v>0.01555630259572048</v>
+        <v>0.0124645541749225</v>
       </c>
     </row>
     <row r="34">
@@ -1999,7 +1999,7 @@
         <v>3.85904541552857e-05</v>
       </c>
       <c r="K42" t="n">
-        <v>0.002592717099286747</v>
+        <v>0.003116138543730626</v>
       </c>
     </row>
     <row r="43">
